--- a/BWI/bestwine_output/bestwine_Peru.xlsx
+++ b/BWI/bestwine_output/bestwine_Peru.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA199"/>
+  <dimension ref="A1:AA200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -21284,6 +21284,99 @@
         </is>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Delitalia Peru S.a.c.</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Delitalia Peru S.a.c.</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>122572</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Lima</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>AV. Primavera 1839. Int. #102, Santiago de Surco, Peru, 15023</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>15023</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>https://delitalia.pe</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr"/>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>ventas@delitalia.pe</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="inlineStr"/>
+      <c r="P200" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
+          <t>20604391548</t>
+        </is>
+      </c>
+      <c r="R200" s="2" t="inlineStr"/>
+      <c r="S200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Delitaliaperu/</t>
+        </is>
+      </c>
+      <c r="T200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delitaliaperu/</t>
+        </is>
+      </c>
+      <c r="U200" s="2" t="inlineStr"/>
+      <c r="V200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@delitaliaperu6914</t>
+        </is>
+      </c>
+      <c r="W200" s="2" t="inlineStr"/>
+      <c r="X200" s="2" t="inlineStr"/>
+      <c r="Y200" s="2" t="inlineStr"/>
+      <c r="Z200" s="2" t="inlineStr"/>
+      <c r="AA200" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Peru.xlsx
+++ b/BWI/bestwine_output/bestwine_Peru.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA200"/>
+  <dimension ref="A1:AA204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -21377,6 +21377,406 @@
       <c r="Z200" s="2" t="inlineStr"/>
       <c r="AA200" s="2" t="inlineStr"/>
     </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Diverchopp</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Diverchopp</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>85558</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Miraflores</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Municipalidad Metropolitana de Lima, Provincia de Lima</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>178 Wiese</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>15046</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.diverchopp.com</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr"/>
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="2" t="inlineStr"/>
+      <c r="M201" s="2" t="inlineStr"/>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>diverchopp@gmail.com</t>
+        </is>
+      </c>
+      <c r="O201" s="2" t="inlineStr"/>
+      <c r="P201" s="2" t="inlineStr"/>
+      <c r="Q201" s="2" t="inlineStr"/>
+      <c r="R201" s="2" t="inlineStr"/>
+      <c r="S201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DiverChopp</t>
+        </is>
+      </c>
+      <c r="T201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/diverchopp/</t>
+        </is>
+      </c>
+      <c r="U201" s="2" t="inlineStr"/>
+      <c r="V201" s="2" t="inlineStr"/>
+      <c r="W201" s="2" t="inlineStr">
+        <is>
+          <t>Martin Salas</t>
+        </is>
+      </c>
+      <c r="X201" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y201" s="2" t="inlineStr"/>
+      <c r="Z201" s="2" t="inlineStr"/>
+      <c r="AA201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/martin-salas-560403188/?originalSubdomain=pe</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Corporación Vega</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Corporación Vega</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>85774</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>Comas</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>198 Avenida Victor Andrés Belaunde</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>15312</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vega.pe</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr"/>
+      <c r="K202" s="2" t="inlineStr"/>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="inlineStr"/>
+      <c r="N202" s="2" t="inlineStr">
+        <is>
+          <t>atencionalcliente@corporacionvega.pe</t>
+        </is>
+      </c>
+      <c r="O202" s="2" t="inlineStr"/>
+      <c r="P202" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q202" s="2" t="inlineStr">
+        <is>
+          <t>20605149937</t>
+        </is>
+      </c>
+      <c r="R202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/corporacion-vega/</t>
+        </is>
+      </c>
+      <c r="S202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/tiendasvegaperu</t>
+        </is>
+      </c>
+      <c r="T202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tiendasvega</t>
+        </is>
+      </c>
+      <c r="U202" s="2" t="inlineStr"/>
+      <c r="V202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCyM_cwwtdfIvNx2KjXIotGQ</t>
+        </is>
+      </c>
+      <c r="W202" s="2" t="inlineStr">
+        <is>
+          <t>Jerson Vega</t>
+        </is>
+      </c>
+      <c r="X202" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y202" s="2" t="inlineStr"/>
+      <c r="Z202" s="2" t="inlineStr"/>
+      <c r="AA202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jerson-vega/</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Corporación Vega</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Corporación Vega</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>85774</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>Comas</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Lima, Lima</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>198 Avenida Victor Andrés Belaunde</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>15312</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vega.pe</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr"/>
+      <c r="K203" s="2" t="inlineStr"/>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="inlineStr"/>
+      <c r="N203" s="2" t="inlineStr">
+        <is>
+          <t>atencionalcliente@corporacionvega.pe</t>
+        </is>
+      </c>
+      <c r="O203" s="2" t="inlineStr"/>
+      <c r="P203" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q203" s="2" t="inlineStr">
+        <is>
+          <t>20605149937</t>
+        </is>
+      </c>
+      <c r="R203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/corporacion-vega/</t>
+        </is>
+      </c>
+      <c r="S203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/tiendasvegaperu</t>
+        </is>
+      </c>
+      <c r="T203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tiendasvega</t>
+        </is>
+      </c>
+      <c r="U203" s="2" t="inlineStr"/>
+      <c r="V203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCyM_cwwtdfIvNx2KjXIotGQ</t>
+        </is>
+      </c>
+      <c r="W203" s="2" t="inlineStr">
+        <is>
+          <t>Luis Cardenas</t>
+        </is>
+      </c>
+      <c r="X203" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Assistant</t>
+        </is>
+      </c>
+      <c r="Y203" s="2" t="inlineStr"/>
+      <c r="Z203" s="2" t="inlineStr"/>
+      <c r="AA203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luis-cardenas-445b44aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Delitalia Peru S.a.c.</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Delitalia Peru S.a.c.</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>122572</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Lima</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>AV. Primavera 1839. Int. #102, Santiago de Surco, Peru, 15023</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>15023</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>https://delitalia.pe</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr"/>
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr"/>
+      <c r="N204" s="2" t="inlineStr">
+        <is>
+          <t>ventas@delitalia.pe</t>
+        </is>
+      </c>
+      <c r="O204" s="2" t="inlineStr"/>
+      <c r="P204" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
+          <t>20604391548</t>
+        </is>
+      </c>
+      <c r="R204" s="2" t="inlineStr"/>
+      <c r="S204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Delitaliaperu/</t>
+        </is>
+      </c>
+      <c r="T204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delitaliaperu/</t>
+        </is>
+      </c>
+      <c r="U204" s="2" t="inlineStr"/>
+      <c r="V204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@delitaliaperu6914</t>
+        </is>
+      </c>
+      <c r="W204" s="2" t="inlineStr"/>
+      <c r="X204" s="2" t="inlineStr"/>
+      <c r="Y204" s="2" t="inlineStr"/>
+      <c r="Z204" s="2" t="inlineStr"/>
+      <c r="AA204" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
